--- a/sum.var_AMR_EHPAD_C3G_R.xlsx
+++ b/sum.var_AMR_EHPAD_C3G_R.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="57" uniqueCount="57">
   <si>
     <t xml:space="preserve"/>
   </si>
@@ -68,15 +68,69 @@
     <t xml:space="preserve">log_AMC_ville_tot_except_FQ</t>
   </si>
   <si>
+    <t xml:space="preserve">AMR_EHPAD_C3G_R.1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_animaux_compagnie_amoxi_clav_R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_animaux_production_C3G_R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_animaux_production_FQ_R</t>
+  </si>
+  <si>
+    <t xml:space="preserve">veto_by_CV</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tx_possession_chats</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tx_possession_chevaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tx_possession_chiens</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_ovins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_veaux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">log_UGB_density_volailles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i007b_part_agribio_surf</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_EHPAD_C3G_R.2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_NO2_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_O3_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_PM10_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">air_PM25_pop</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dju_refroi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AMR_EHPAD_C3G_R.3</t>
+  </si>
+  <si>
     <t xml:space="preserve">log_i041_pib_hab</t>
   </si>
   <si>
     <t xml:space="preserve">prop_travail_manuel</t>
   </si>
   <si>
-    <t xml:space="preserve">veto_by_CV</t>
-  </si>
-  <si>
     <t xml:space="preserve">APL_medG</t>
   </si>
   <si>
@@ -89,46 +143,10 @@
     <t xml:space="preserve">couv_creche</t>
   </si>
   <si>
-    <t xml:space="preserve">tx_possession_chats</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tx_possession_chevaux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tx_possession_chiens</t>
-  </si>
-  <si>
     <t xml:space="preserve">pop_75_plus_prop</t>
   </si>
   <si>
     <t xml:space="preserve">log_pop_density</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air_NO2_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air_O3_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air_PM10_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">air_PM25_pop</t>
-  </si>
-  <si>
-    <t xml:space="preserve">dju_refroi</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_ovins</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_veaux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">log_UGB_density_volailles</t>
-  </si>
-  <si>
-    <t xml:space="preserve">i007b_part_agribio_surf</t>
   </si>
   <si>
     <t xml:space="preserve">Auvergne-Rhone-Alpes</t>
@@ -611,1433 +629,1667 @@
       <c r="AM1" t="s">
         <v>38</v>
       </c>
+      <c r="AN1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>41</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>42</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>43</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="B2" t="n">
-        <v>-0.0125313999235648</v>
+        <v>-0.00429165569474729</v>
       </c>
       <c r="C2" t="n">
-        <v>0.00533223778199618</v>
+        <v>-0.0332116974675727</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0227989866658787</v>
+        <v>0.00673395387442586</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.0760709390872229</v>
+        <v>-0.0236791454821986</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.00713689493866628</v>
+        <v>-0.0757500947291418</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.0778575670354554</v>
+        <v>-0.102978962370727</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0101678706021108</v>
+        <v>-0.0519636488636131</v>
       </c>
       <c r="I2" t="n">
-        <v>0.12117932925202</v>
+        <v>0.10036063159044</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.0808807125717539</v>
+        <v>0.0335610808107989</v>
       </c>
       <c r="K2" t="n">
-        <v>0.0813375519024485</v>
+        <v>0.045746548313324</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.166150175030627</v>
+        <v>-0.119218369487267</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.0938456383753946</v>
+        <v>-0.0899670434204568</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0753099080728623</v>
+        <v>-0.0729740524328948</v>
       </c>
       <c r="O2" t="n">
-        <v>-0.0219646884996701</v>
+        <v>-0.0500340516551097</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.122122632657002</v>
+        <v>-0.11340677064681</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.00837664740857373</v>
+        <v>-0.0580919365243204</v>
       </c>
       <c r="R2" t="n">
-        <v>-0.122857714317659</v>
+        <v>-0.114851315499916</v>
       </c>
       <c r="S2" t="n">
-        <v>0.0516394578746546</v>
+        <v>-0.00429165569474729</v>
       </c>
       <c r="T2" t="n">
-        <v>0.013549101832271</v>
+        <v>0.0615986685381392</v>
       </c>
       <c r="U2" t="n">
-        <v>0.259298879221153</v>
+        <v>-0.0057397080210425</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.132075270155748</v>
+        <v>-0.0117322731793835</v>
       </c>
       <c r="W2" t="n">
-        <v>0.149346773238414</v>
+        <v>0.0582695830019245</v>
       </c>
       <c r="X2" t="n">
-        <v>0.00170010725214271</v>
+        <v>-12.3303494649166</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.0152766041698991</v>
+        <v>-4.38486917941033</v>
       </c>
       <c r="Z2" t="n">
-        <v>-13.486116235373</v>
+        <v>-18.8678731402826</v>
       </c>
       <c r="AA2" t="n">
-        <v>-4.61322345210427</v>
+        <v>0.150973298446975</v>
       </c>
       <c r="AB2" t="n">
-        <v>-16.3899683786656</v>
+        <v>0.235349613528001</v>
       </c>
       <c r="AC2" t="n">
-        <v>-0.00429661533147272</v>
+        <v>-0.209548982113039</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.0642559185586429</v>
+        <v>0.00239386743473404</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.49498460134298</v>
+        <v>-0.00429165569474729</v>
       </c>
       <c r="AF2" t="n">
-        <v>-3.1629388150638</v>
+        <v>2.46131616730103</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.188862103365707</v>
+        <v>-2.19227167052624</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.657771400481362</v>
+        <v>-0.14689466098425</v>
       </c>
       <c r="AI2" t="n">
-        <v>3.04099299782066</v>
+        <v>0.464358721866095</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.152726803806079</v>
+        <v>11.0218902694913</v>
       </c>
       <c r="AK2" t="n">
-        <v>0.265470471835774</v>
+        <v>-0.00429165569474729</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.201469048623079</v>
+        <v>0.0711842396775379</v>
       </c>
       <c r="AM2" t="n">
-        <v>-0.00738622746770978</v>
+        <v>0.0133997267485429</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>-0.23814057256977</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>0.102157056829545</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>-0.0032360124396595</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.010521087269544</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>-0.00508228708977854</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>-0.073997723673461</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.040666297693938</v>
+        <v>-0.0402186791401152</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.044306645770397</v>
+        <v>-0.0269866252159834</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.0467451233262862</v>
+        <v>-0.0626853491315937</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.0206987396103455</v>
+        <v>0.0667609974418947</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.0049694833497094</v>
+        <v>0.00896430553400415</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.0778980250134365</v>
+        <v>0.0402110528836817</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.00255417970736954</v>
+        <v>0.0110822982171971</v>
       </c>
       <c r="I3" t="n">
-        <v>0.111029354540155</v>
+        <v>0.0352159793973484</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.0266083859129174</v>
+        <v>-0.0975259174762126</v>
       </c>
       <c r="K3" t="n">
-        <v>0.135613926142571</v>
+        <v>0.0890607105496024</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.00256164215613753</v>
+        <v>0.0302138660849762</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.0209951265275466</v>
+        <v>-0.0164060544761927</v>
       </c>
       <c r="N3" t="n">
-        <v>0.0103011226207277</v>
+        <v>0.0138953877725435</v>
       </c>
       <c r="O3" t="n">
-        <v>0.0435210118653462</v>
+        <v>0.0264843564568429</v>
       </c>
       <c r="P3" t="n">
-        <v>-0.0011313276221727</v>
+        <v>0.0155037622756563</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.00281244967733614</v>
+        <v>0.0187351769509707</v>
       </c>
       <c r="R3" t="n">
-        <v>-0.00198693942446345</v>
+        <v>0.0175382891813646</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.121769049849203</v>
+        <v>-0.0402186791401152</v>
       </c>
       <c r="T3" t="n">
-        <v>0.0395477376111578</v>
+        <v>0.0176599543658448</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.949487629574545</v>
+        <v>-0.00594697343484887</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.0793069585208478</v>
+        <v>0.00718843060368204</v>
       </c>
       <c r="W3" t="n">
-        <v>-0.421974144262473</v>
+        <v>-0.770302815554919</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.0153332644089001</v>
+        <v>3.17771325978908</v>
       </c>
       <c r="Y3" t="n">
-        <v>-0.0150643309190375</v>
+        <v>9.45590659332335</v>
       </c>
       <c r="Z3" t="n">
-        <v>9.91940407536402</v>
+        <v>15.5290344904718</v>
       </c>
       <c r="AA3" t="n">
-        <v>9.2266987954408</v>
+        <v>-0.191019448211413</v>
       </c>
       <c r="AB3" t="n">
-        <v>18.7141922392619</v>
+        <v>0.323806812980551</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.00970917416126822</v>
+        <v>-0.671327616035061</v>
       </c>
       <c r="AD3" t="n">
-        <v>-0.752378848450291</v>
+        <v>-0.0109444588619368</v>
       </c>
       <c r="AE3" t="n">
-        <v>-1.3695336311812</v>
+        <v>-0.0402186791401152</v>
       </c>
       <c r="AF3" t="n">
-        <v>-0.251602225656889</v>
+        <v>-1.78849019467855</v>
       </c>
       <c r="AG3" t="n">
-        <v>-1.68261929819898</v>
+        <v>0.594774917323201</v>
       </c>
       <c r="AH3" t="n">
-        <v>-1.08398984254274</v>
+        <v>-1.71738724827605</v>
       </c>
       <c r="AI3" t="n">
-        <v>-55.8608537531482</v>
+        <v>-0.472378788154204</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.197013925810543</v>
+        <v>-5.42457052529447</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.338855562043724</v>
+        <v>-0.0402186791401152</v>
       </c>
       <c r="AL3" t="n">
-        <v>-0.656730869945827</v>
+        <v>-0.124494038406793</v>
       </c>
       <c r="AM3" t="n">
-        <v>-0.01265879388501</v>
+        <v>0.0396977072599543</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>-0.0900985847101783</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>-0.430405702605618</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>-0.00921892180210863</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>-0.0209620918427937</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.00960011029148658</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>-0.733223676197547</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="B4" t="n">
-        <v>-0.0127787896932164</v>
+        <v>-0.0187604854619429</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.0129134051303526</v>
+        <v>0.00779730675007682</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.140746470953964</v>
+        <v>-0.0839658046014768</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.183617970931607</v>
+        <v>-0.160573643927154</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.00624257076815509</v>
+        <v>0.0116350506174326</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0894239027457871</v>
+        <v>0.201525623572652</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.034263995654798</v>
+        <v>-0.0181058995709713</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.343476301081051</v>
+        <v>-0.278648268623139</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.648958375030392</v>
+        <v>-0.37338220636912</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.239566660996442</v>
+        <v>-0.204154783015747</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.203943722301149</v>
+        <v>-0.141210710616172</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0896758285452184</v>
+        <v>-0.0466720427614512</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.0198286805785976</v>
+        <v>-0.0223308923262131</v>
       </c>
       <c r="O4" t="n">
-        <v>0.0372808599486151</v>
+        <v>0.0503303137154591</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.118308536640616</v>
+        <v>-0.0794524172790022</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.0210752010592698</v>
+        <v>-0.00749851703955117</v>
       </c>
       <c r="R4" t="n">
-        <v>-0.113510835517452</v>
+        <v>-0.0732747438842462</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0434355780501073</v>
+        <v>-0.0187604854619429</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0188477005491508</v>
+        <v>-0.0697061783083387</v>
       </c>
       <c r="U4" t="n">
-        <v>0.00764017624437827</v>
+        <v>-0.00184761400226204</v>
       </c>
       <c r="V4" t="n">
-        <v>0.415098497866289</v>
+        <v>-0.0100046443402444</v>
       </c>
       <c r="W4" t="n">
-        <v>0.361199868945771</v>
+        <v>-0.0055179876751338</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.009857242596429</v>
+        <v>-3.63618198377684</v>
       </c>
       <c r="Y4" t="n">
-        <v>-0.0533366474791847</v>
+        <v>3.19198075695889</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.414739378189368</v>
+        <v>12.7284237561243</v>
       </c>
       <c r="AA4" t="n">
-        <v>3.12226466929884</v>
+        <v>-0.369642789809718</v>
       </c>
       <c r="AB4" t="n">
-        <v>8.52678975713118</v>
+        <v>0.75630921144054</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.00498102000926593</v>
+        <v>2.08339580005781</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.00800516866178649</v>
+        <v>-0.00656637404658737</v>
       </c>
       <c r="AE4" t="n">
-        <v>-3.09848283142649</v>
+        <v>-0.0187604854619429</v>
       </c>
       <c r="AF4" t="n">
-        <v>4.70192221616382</v>
+        <v>-4.31875399729239</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.277708554007333</v>
+        <v>3.56540005694909</v>
       </c>
       <c r="AH4" t="n">
-        <v>-0.707608792389346</v>
+        <v>-0.782589675263861</v>
       </c>
       <c r="AI4" t="n">
-        <v>-31.4648541764182</v>
+        <v>-1.41801144666476</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.349755156107614</v>
+        <v>-42.063917768553</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.675910715068681</v>
+        <v>-0.0187604854619429</v>
       </c>
       <c r="AL4" t="n">
-        <v>2.04909981524149</v>
+        <v>-0.0654341902052057</v>
       </c>
       <c r="AM4" t="n">
-        <v>-0.0118015130465163</v>
+        <v>0.0180099487089462</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.271938752196663</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.0988875903309765</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>-0.00176396245312178</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>-0.041946136308274</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.00639467520062348</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>-0.00507901594179504</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.0348394447391905</v>
+        <v>-0.0326270606944119</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.125115591104955</v>
+        <v>-0.122014764713604</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.106863944176263</v>
+        <v>-0.0980898804713043</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0833846795753841</v>
+        <v>-0.0460995270754599</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.108325923110666</v>
+        <v>-0.0856219006310501</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.308814558245972</v>
+        <v>-0.169157530573119</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.128658607126521</v>
+        <v>-0.0943666974336294</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.0525230084274329</v>
+        <v>-0.046366232871423</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.103793338622981</v>
+        <v>-0.130678648965293</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.0737045122649883</v>
+        <v>-0.048917726788189</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.0681564288574071</v>
+        <v>-0.0692464942458135</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.0684748997840217</v>
+        <v>-0.0647205616522289</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0558567786530947</v>
+        <v>-0.0278724541611876</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0312567695357522</v>
+        <v>-0.0218776303200323</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.0681493626463667</v>
+        <v>-0.0651659970916472</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.127559561479405</v>
+        <v>-0.094704517426158</v>
       </c>
       <c r="R5" t="n">
-        <v>-0.0719304102850721</v>
+        <v>-0.0662767394077226</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.128476606361307</v>
+        <v>-0.0326270606944119</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0246518889904745</v>
+        <v>-0.0737977140278657</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.916809250734647</v>
+        <v>0.0108436371775343</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.588779331562012</v>
+        <v>0.0064511956297064</v>
       </c>
       <c r="W5" t="n">
-        <v>-0.965860492276028</v>
+        <v>-0.602380310114915</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.0112572594306242</v>
+        <v>12.8592769993275</v>
       </c>
       <c r="Y5" t="n">
-        <v>-0.0431754152079666</v>
+        <v>-0.192251643736603</v>
       </c>
       <c r="Z5" t="n">
-        <v>14.9074838384816</v>
+        <v>26.77912495624</v>
       </c>
       <c r="AA5" t="n">
-        <v>-0.22118721461674</v>
+        <v>-0.284096832305203</v>
       </c>
       <c r="AB5" t="n">
-        <v>23.6074266723268</v>
+        <v>-0.416594915570839</v>
       </c>
       <c r="AC5" t="n">
-        <v>0.00797081689478737</v>
+        <v>-0.311494422645666</v>
       </c>
       <c r="AD5" t="n">
-        <v>-0.636638658744777</v>
+        <v>-0.0482426004035456</v>
       </c>
       <c r="AE5" t="n">
-        <v>-2.50159326171497</v>
+        <v>-0.0326270606944119</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1.06292799774263</v>
+        <v>-3.27804295023073</v>
       </c>
       <c r="AG5" t="n">
-        <v>-1.57155066518468</v>
+        <v>0.103643179064499</v>
       </c>
       <c r="AH5" t="n">
-        <v>-0.20146051900081</v>
+        <v>-1.31587084830012</v>
       </c>
       <c r="AI5" t="n">
-        <v>-52.2257037571435</v>
+        <v>-0.38010878600959</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-0.252489798850181</v>
+        <v>-6.61747476724499</v>
       </c>
       <c r="AK5" t="n">
-        <v>-0.402523463228813</v>
+        <v>-0.0326270606944119</v>
       </c>
       <c r="AL5" t="n">
-        <v>-0.195025553176616</v>
+        <v>-0.0889789398903094</v>
       </c>
       <c r="AM5" t="n">
-        <v>-0.069240460431635</v>
+        <v>0.0267904630273537</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>-0.498774154428945</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>-0.805735820374807</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>0.00440535712346129</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-0.0302881325843596</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.00829966907346026</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>-0.622655757258443</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="B6" t="n">
-        <v>-0.0182845620891627</v>
+        <v>-0.0138046454332127</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0480727881233197</v>
+        <v>0.110123897161324</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0866387638384615</v>
+        <v>0.0594823394641421</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.103825701929883</v>
+        <v>0.00138620103745199</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0308543324964791</v>
+        <v>-0.0410338671533221</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0353421962176599</v>
+        <v>-0.0524689124097606</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0313537320102507</v>
+        <v>-0.00777819389424965</v>
       </c>
       <c r="I6" t="n">
-        <v>0.149795514321296</v>
+        <v>0.183072132285433</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.200758928243766</v>
+        <v>-0.0140515295826258</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0653240924236424</v>
+        <v>0.085549861147115</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0203662392806378</v>
+        <v>0.0594315464166114</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.00259875943139501</v>
+        <v>-0.0139516952096968</v>
       </c>
       <c r="N6" t="n">
-        <v>0.0202523188310269</v>
+        <v>0.0972308094678789</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.026491340656869</v>
+        <v>-0.0395915370136168</v>
       </c>
       <c r="P6" t="n">
-        <v>0.00962550713235052</v>
+        <v>0.0291116808889536</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.0452390041256079</v>
+        <v>-0.0130612761644817</v>
       </c>
       <c r="R6" t="n">
-        <v>0.00579318208056581</v>
+        <v>0.0248295369766438</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0969276646772585</v>
+        <v>-0.0138046454332127</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0176522562807752</v>
+        <v>0.0389302205968238</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.819762691244818</v>
+        <v>0.0145774880585199</v>
       </c>
       <c r="V6" t="n">
-        <v>0.155428919578729</v>
+        <v>-0.000123590283420022</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.219544013778863</v>
+        <v>-0.423678741868557</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.00336734958909263</v>
+        <v>-2.61132807038946</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0348548143041566</v>
+        <v>-6.89076795398724</v>
       </c>
       <c r="Z6" t="n">
-        <v>-2.21113518733343</v>
+        <v>-29.9470519040486</v>
       </c>
       <c r="AA6" t="n">
-        <v>-6.67775622543959</v>
+        <v>-0.150794157450055</v>
       </c>
       <c r="AB6" t="n">
-        <v>-26.0751678818911</v>
+        <v>-0.0224633016088872</v>
       </c>
       <c r="AC6" t="n">
-        <v>-0.00745795120297978</v>
+        <v>-0.595670602562299</v>
       </c>
       <c r="AD6" t="n">
-        <v>-0.25722513596181</v>
+        <v>-0.0287033067680863</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.0549245784640871</v>
+        <v>-0.0138046454332127</v>
       </c>
       <c r="AF6" t="n">
-        <v>-2.28307705009712</v>
+        <v>0.647163158559724</v>
       </c>
       <c r="AG6" t="n">
-        <v>-1.00049179053382</v>
+        <v>-3.1904011933925</v>
       </c>
       <c r="AH6" t="n">
-        <v>-0.751013983466864</v>
+        <v>-0.453595963951475</v>
       </c>
       <c r="AI6" t="n">
-        <v>-72.5190584647254</v>
+        <v>0.622946781722748</v>
       </c>
       <c r="AJ6" t="n">
-        <v>-0.161548425346817</v>
+        <v>-15.8994468340273</v>
       </c>
       <c r="AK6" t="n">
-        <v>-0.0303317003394657</v>
+        <v>-0.0138046454332127</v>
       </c>
       <c r="AL6" t="n">
-        <v>-0.477447968355574</v>
+        <v>-0.0879917342022967</v>
       </c>
       <c r="AM6" t="n">
-        <v>-0.0357556707977117</v>
+        <v>0.0198687079575747</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>0.0877323322809686</v>
+      </c>
+      <c r="AO6" t="n">
+        <v>-0.190653634970529</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>0.00219232762744595</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.0118321019448495</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>-0.00593181281709199</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>-0.242091355144987</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="B7" t="n">
-        <v>0.00286982841071415</v>
+        <v>0.0502696712121473</v>
       </c>
       <c r="C7" t="n">
-        <v>0.127520428967189</v>
+        <v>0.0554788106625309</v>
       </c>
       <c r="D7" t="n">
-        <v>0.173274163425219</v>
+        <v>0.0614207298724778</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0285967329455456</v>
+        <v>-0.0145088813068838</v>
       </c>
       <c r="F7" t="n">
-        <v>0.141630383776783</v>
+        <v>0.110606121684165</v>
       </c>
       <c r="G7" t="n">
-        <v>0.148977636540644</v>
+        <v>0.0680502058653062</v>
       </c>
       <c r="H7" t="n">
-        <v>0.159760201884033</v>
+        <v>0.0918115939259928</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0536157157528258</v>
+        <v>0.0601744798308835</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.0261523399039344</v>
+        <v>-0.188331569638821</v>
       </c>
       <c r="K7" t="n">
-        <v>0.0809305374955791</v>
+        <v>0.0406597387657337</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0829862113056558</v>
+        <v>0.0874935060532407</v>
       </c>
       <c r="M7" t="n">
-        <v>0.133798044136127</v>
+        <v>0.110979265869809</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0533242943046529</v>
+        <v>0.0239107660601627</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.0366594319439549</v>
+        <v>0.00273469106055817</v>
       </c>
       <c r="P7" t="n">
-        <v>0.123952887678216</v>
+        <v>0.105554071475889</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.154176613298323</v>
+        <v>0.0951759245750315</v>
       </c>
       <c r="R7" t="n">
-        <v>0.129365364213217</v>
+        <v>0.111511245163811</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.130848673943125</v>
+        <v>0.0502696712121473</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.0107484999537953</v>
+        <v>-0.0184311770127115</v>
       </c>
       <c r="U7" t="n">
-        <v>0.179848586018995</v>
+        <v>-0.000652098137484839</v>
       </c>
       <c r="V7" t="n">
-        <v>0.392105643161906</v>
+        <v>-0.0064557992462484</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.634437889386094</v>
+        <v>0.138826687668009</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.0245910786560118</v>
+        <v>-4.93482380993126</v>
       </c>
       <c r="Y7" t="n">
-        <v>-0.0403763103815386</v>
+        <v>-7.22063560926808</v>
       </c>
       <c r="Z7" t="n">
-        <v>-4.33805641088596</v>
+        <v>19.8455533951558</v>
       </c>
       <c r="AA7" t="n">
-        <v>-6.88002678723866</v>
+        <v>-0.271578415094269</v>
       </c>
       <c r="AB7" t="n">
-        <v>19.4952182636717</v>
+        <v>0.159101834134017</v>
       </c>
       <c r="AC7" t="n">
-        <v>-0.0197544909838502</v>
+        <v>0.197995368697023</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.403806605660791</v>
+        <v>-0.0626469474552824</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.10444105982622</v>
+        <v>0.0502696712121473</v>
       </c>
       <c r="AF7" t="n">
-        <v>-4.91147936220112</v>
+        <v>1.12134033295021</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.25840219635609</v>
+        <v>-5.94298722785559</v>
       </c>
       <c r="AH7" t="n">
-        <v>0.637872949977439</v>
+        <v>2.15545868450043</v>
       </c>
       <c r="AI7" t="n">
-        <v>-65.5738121330756</v>
+        <v>1.54602068082667</v>
       </c>
       <c r="AJ7" t="n">
-        <v>-0.256817404185684</v>
+        <v>-32.1995523411849</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.162015776947522</v>
+        <v>0.0502696712121473</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.296184066760388</v>
+        <v>-0.130900303696153</v>
       </c>
       <c r="AM7" t="n">
-        <v>-0.0886957729746736</v>
+        <v>-0.0097474141827183</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>0.357638558366775</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>-0.563513299647262</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0.00207569704984946</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>-0.0501937303954304</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>-0.0185588523633794</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>0.420820327277151</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0758471680096951</v>
+        <v>0.0701513610598374</v>
       </c>
       <c r="C8" t="n">
-        <v>-0.0994317984299556</v>
+        <v>-0.134831925330972</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.0761982067032024</v>
+        <v>-0.106665696028367</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.0443218255085664</v>
+        <v>-0.00210520011203225</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.0474864701729299</v>
+        <v>-0.0041952574902393</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0261849816600726</v>
+        <v>-0.0259083380395657</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.0872531706793886</v>
+        <v>-0.0493917054781802</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0320282106069829</v>
+        <v>-0.0883645155060498</v>
       </c>
       <c r="J8" t="n">
-        <v>0.285066640625593</v>
+        <v>0.309219299525867</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0453591787073651</v>
+        <v>0.0567337331081234</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0561470107958103</v>
+        <v>0.0138111941148235</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0968056848936301</v>
+        <v>0.0861825699207249</v>
       </c>
       <c r="N8" t="n">
-        <v>0.308860302034807</v>
+        <v>0.263100653547779</v>
       </c>
       <c r="O8" t="n">
-        <v>0.0417192033632819</v>
+        <v>0.0241502037875185</v>
       </c>
       <c r="P8" t="n">
-        <v>0.107748297219291</v>
+        <v>0.0823716821161474</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.0858079143900958</v>
+        <v>-0.0423401208623003</v>
       </c>
       <c r="R8" t="n">
-        <v>0.117006518966685</v>
+        <v>0.0918117366690664</v>
       </c>
       <c r="S8" t="n">
-        <v>0.573783024870932</v>
+        <v>0.0701513610598374</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.101548228441481</v>
+        <v>-0.0180170457820621</v>
       </c>
       <c r="U8" t="n">
-        <v>2.15055758762769</v>
+        <v>-0.00203471874096844</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.522351338233364</v>
+        <v>-0.00704514598014381</v>
       </c>
       <c r="W8" t="n">
-        <v>0.65397987258603</v>
+        <v>1.71905337412741</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.0145537868518684</v>
+        <v>-9.01272307721351</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.111785208040009</v>
+        <v>-16.3377612856515</v>
       </c>
       <c r="Z8" t="n">
-        <v>-23.3739920690954</v>
+        <v>-92.0387708878531</v>
       </c>
       <c r="AA8" t="n">
-        <v>-15.8110445136442</v>
+        <v>-0.537245017539383</v>
       </c>
       <c r="AB8" t="n">
-        <v>-92.0611796927019</v>
+        <v>-1.22631695627796</v>
       </c>
       <c r="AC8" t="n">
-        <v>-0.0297342066620386</v>
+        <v>-0.810419476847576</v>
       </c>
       <c r="AD8" t="n">
-        <v>2.10118375622467</v>
+        <v>-0.0360635327910034</v>
       </c>
       <c r="AE8" t="n">
-        <v>8.26736980387867</v>
+        <v>0.0701513610598374</v>
       </c>
       <c r="AF8" t="n">
-        <v>-5.52486089049018</v>
+        <v>11.0611048510848</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.42896583509715</v>
+        <v>-8.13657157043532</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.22097937624756</v>
+        <v>1.89965622981696</v>
       </c>
       <c r="AI8" t="n">
-        <v>-59.7466680389308</v>
+        <v>1.2231669853248</v>
       </c>
       <c r="AJ8" t="n">
-        <v>-0.515552577646136</v>
+        <v>-14.3772288344109</v>
       </c>
       <c r="AK8" t="n">
-        <v>-1.18491441224505</v>
+        <v>0.0701513610598374</v>
       </c>
       <c r="AL8" t="n">
-        <v>-0.709160811419627</v>
+        <v>0.623368914024887</v>
       </c>
       <c r="AM8" t="n">
-        <v>-0.039425202884282</v>
+        <v>-0.104572526869896</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>-0.364227869492569</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>0.868083983240932</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>-0.024163270529116</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.103648576807794</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>-0.0301335771134524</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>2.10000862327134</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.0262277105584639</v>
+        <v>-0.0394092032697747</v>
       </c>
       <c r="C9" t="n">
-        <v>0.137826934791419</v>
+        <v>0.0694253778846952</v>
       </c>
       <c r="D9" t="n">
-        <v>0.066864101862825</v>
+        <v>0.0346589884140389</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0994395899840363</v>
+        <v>0.111605333198221</v>
       </c>
       <c r="F9" t="n">
-        <v>0.131407276379609</v>
+        <v>0.0962525363404283</v>
       </c>
       <c r="G9" t="n">
-        <v>0.0539815833420412</v>
+        <v>-0.00746862204342071</v>
       </c>
       <c r="H9" t="n">
-        <v>0.11219748725924</v>
+        <v>0.0855536155303945</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0127262086767501</v>
+        <v>0.0504734259398501</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0553671062272829</v>
+        <v>-0.208271122741779</v>
       </c>
       <c r="K9" t="n">
-        <v>0.178641490445863</v>
+        <v>0.0986245611203094</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0417892534060859</v>
+        <v>0.0786633420934962</v>
       </c>
       <c r="M9" t="n">
-        <v>0.0542306462131388</v>
+        <v>0.0415623718171625</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.019218511581013</v>
+        <v>-0.0324191136737228</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.0280829607399335</v>
+        <v>-0.0027053805893549</v>
       </c>
       <c r="P9" t="n">
-        <v>0.0470995087582011</v>
+        <v>0.0383287535447493</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.114592524641011</v>
+        <v>0.09066077539429</v>
       </c>
       <c r="R9" t="n">
-        <v>0.0486946919350665</v>
+        <v>0.0416848994848347</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.0851388989416012</v>
+        <v>-0.0394092032697747</v>
       </c>
       <c r="T9" t="n">
-        <v>0.0328469659685514</v>
+        <v>0.0153132104459661</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.435925064440227</v>
+        <v>-0.000969293831558328</v>
       </c>
       <c r="V9" t="n">
-        <v>0.0470364211183201</v>
+        <v>-0.00545927080555194</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.601602770183393</v>
+        <v>-0.314908419026853</v>
       </c>
       <c r="X9" t="n">
-        <v>0.00368077136245292</v>
+        <v>-0.624784079803963</v>
       </c>
       <c r="Y9" t="n">
-        <v>-0.0532911174132354</v>
+        <v>24.7971160064304</v>
       </c>
       <c r="Z9" t="n">
-        <v>1.01751672069733</v>
+        <v>21.1224527119021</v>
       </c>
       <c r="AA9" t="n">
-        <v>24.9499644763259</v>
+        <v>-0.239068858776235</v>
       </c>
       <c r="AB9" t="n">
-        <v>23.4564037232326</v>
+        <v>0.697195612240213</v>
       </c>
       <c r="AC9" t="n">
-        <v>0.000889349126761045</v>
+        <v>-0.0374455911788562</v>
       </c>
       <c r="AD9" t="n">
-        <v>-0.115903764171673</v>
+        <v>-0.0315474910081037</v>
       </c>
       <c r="AE9" t="n">
-        <v>-0.768125665259879</v>
+        <v>-0.0394092032697747</v>
       </c>
       <c r="AF9" t="n">
-        <v>0.186917479833839</v>
+        <v>-1.67028852900829</v>
       </c>
       <c r="AG9" t="n">
-        <v>-0.513389147401974</v>
+        <v>-0.0109312412913779</v>
       </c>
       <c r="AH9" t="n">
-        <v>0.151057613194073</v>
+        <v>-0.191921675231057</v>
       </c>
       <c r="AI9" t="n">
-        <v>-56.4837095748711</v>
+        <v>-0.336248048840461</v>
       </c>
       <c r="AJ9" t="n">
-        <v>-0.264646712670871</v>
+        <v>-38.3424138223202</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.678087550358818</v>
+        <v>-0.0394092032697747</v>
       </c>
       <c r="AL9" t="n">
-        <v>-0.0300025543366282</v>
+        <v>-0.085804112752481</v>
       </c>
       <c r="AM9" t="n">
-        <v>-0.048765775507631</v>
+        <v>0.0321586612015137</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>-0.0206447053958451</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>-0.56047013214129</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>-0.0168108341459025</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>-0.0496410442958685</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.000208184884516435</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>-0.10211662579286</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>47</v>
+        <v>53</v>
       </c>
       <c r="B10" t="n">
-        <v>-0.0196887412978049</v>
+        <v>-0.0130458102052142</v>
       </c>
       <c r="C10" t="n">
-        <v>0.119566873605868</v>
+        <v>0.194361998892864</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0580484019414118</v>
+        <v>0.0975994435577037</v>
       </c>
       <c r="E10" t="n">
-        <v>0.00942039501627749</v>
+        <v>0.0233719976102421</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.00833308192360844</v>
+        <v>0.0395856823912233</v>
       </c>
       <c r="G10" t="n">
-        <v>0.114278803718761</v>
+        <v>0.0698733751954535</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0366146007609261</v>
+        <v>0.0705558338791445</v>
       </c>
       <c r="I10" t="n">
-        <v>0.0590881138113237</v>
+        <v>0.0849547857042242</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0770381671136652</v>
+        <v>0.0601430323680632</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.023095940086888</v>
+        <v>0.0292138845299469</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0138250468774766</v>
+        <v>0.00620438066090511</v>
       </c>
       <c r="M10" t="n">
-        <v>0.0296484660345386</v>
+        <v>0.0307882196430586</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0465870670717229</v>
+        <v>-0.0506951096157239</v>
       </c>
       <c r="O10" t="n">
-        <v>0.0498456023731082</v>
+        <v>0.013325731189545</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0281726209203691</v>
+        <v>0.0325507305764863</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.0329231364456873</v>
+        <v>0.0637311713530358</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0258050253660344</v>
+        <v>0.0274333514639498</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0742761836449131</v>
+        <v>-0.0130458102052142</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0049517994584258</v>
+        <v>0.0800068228600296</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.41243639403738</v>
+        <v>-0.00540575234929896</v>
       </c>
       <c r="V10" t="n">
-        <v>0.213089531958767</v>
+        <v>-0.00579879783185996</v>
       </c>
       <c r="W10" t="n">
-        <v>0.393624918490865</v>
+        <v>-0.317730159419209</v>
       </c>
       <c r="X10" t="n">
-        <v>0.012776986436676</v>
+        <v>9.18564175834393</v>
       </c>
       <c r="Y10" t="n">
-        <v>-0.0187614298914516</v>
+        <v>2.60351806295416</v>
       </c>
       <c r="Z10" t="n">
-        <v>11.8084286059017</v>
+        <v>38.9228280039465</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.19475765330046</v>
+        <v>0.598748291963005</v>
       </c>
       <c r="AB10" t="n">
-        <v>38.9198069184191</v>
+        <v>0.0824821535077846</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.0144634747119542</v>
+        <v>0.322043412432475</v>
       </c>
       <c r="AD10" t="n">
-        <v>-0.534930591085958</v>
+        <v>-0.0161333980051841</v>
       </c>
       <c r="AE10" t="n">
-        <v>-2.82939098760496</v>
+        <v>-0.0130458102052142</v>
       </c>
       <c r="AF10" t="n">
-        <v>-0.781407843276192</v>
+        <v>-3.36054905774655</v>
       </c>
       <c r="AG10" t="n">
-        <v>-0.158930441113735</v>
+        <v>0.125640023711585</v>
       </c>
       <c r="AH10" t="n">
-        <v>-0.407920590719671</v>
+        <v>-1.05862112080309</v>
       </c>
       <c r="AI10" t="n">
-        <v>76.4027241779897</v>
+        <v>-0.969569942067806</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.582391899523294</v>
+        <v>20.4716391934634</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.0686123327616333</v>
+        <v>-0.0130458102052142</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.0563851631786323</v>
+        <v>-0.0682606175468987</v>
       </c>
       <c r="AM10" t="n">
-        <v>-0.017420608384215</v>
+        <v>0.00640762906621618</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>0.226721715917034</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.255688366175892</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>0.012959735459373</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.000487602492993006</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.0154679259900934</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>-0.544121789461287</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0266021458313641</v>
+        <v>0.0115876780519277</v>
       </c>
       <c r="C11" t="n">
-        <v>0.00786260282601511</v>
+        <v>0.147380940790155</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0160059031384701</v>
+        <v>0.0860160295965499</v>
       </c>
       <c r="E11" t="n">
-        <v>0.0715283036037904</v>
+        <v>0.02995211991031</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0206132949650322</v>
+        <v>0.00953556340121431</v>
       </c>
       <c r="G11" t="n">
-        <v>0.012254016803493</v>
+        <v>0.0558181981008451</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.0188338187760995</v>
+        <v>0.0296954906944263</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0774082714138076</v>
+        <v>0.0158617624856274</v>
       </c>
       <c r="J11" t="n">
-        <v>0.557782375930676</v>
+        <v>0.313060253546427</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0153157191070746</v>
+        <v>-0.0427652547046527</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0661033386147282</v>
+        <v>0.042769586516405</v>
       </c>
       <c r="M11" t="n">
-        <v>0.0146006837307656</v>
+        <v>0.0211958266043548</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0489044650010751</v>
+        <v>-0.0434899261813493</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.0385971980392365</v>
+        <v>-0.000646349904212877</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0209677708944</v>
+        <v>0.03321280075391</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.0225273286417265</v>
+        <v>0.0240534255699838</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0142927395876646</v>
+        <v>0.0233233898465209</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.108889977288115</v>
+        <v>0.0115876780519277</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0256443485744775</v>
+        <v>-0.0140129434087858</v>
       </c>
       <c r="U11" t="n">
-        <v>0.500460406153616</v>
+        <v>0.0169332582755317</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.0512081488565186</v>
+        <v>0.0533113040488226</v>
       </c>
       <c r="W11" t="n">
-        <v>0.438639498601624</v>
+        <v>0.128949509529747</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0245321466682712</v>
+        <v>6.42513956495643</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0271367628666701</v>
+        <v>-3.78655200623572</v>
       </c>
       <c r="Z11" t="n">
-        <v>8.31036446199816</v>
+        <v>28.9449742236903</v>
       </c>
       <c r="AA11" t="n">
-        <v>-4.00543987240923</v>
+        <v>0.975430705687471</v>
       </c>
       <c r="AB11" t="n">
-        <v>25.9830510915756</v>
+        <v>-0.198475120765655</v>
       </c>
       <c r="AC11" t="n">
-        <v>0.00911457415855695</v>
+        <v>-0.48313178901756</v>
       </c>
       <c r="AD11" t="n">
-        <v>-0.394898992110932</v>
+        <v>0.0595370092343964</v>
       </c>
       <c r="AE11" t="n">
-        <v>-1.27025301167474</v>
+        <v>0.0115876780519277</v>
       </c>
       <c r="AF11" t="n">
-        <v>3.77731543818017</v>
+        <v>-1.42640909208072</v>
       </c>
       <c r="AG11" t="n">
-        <v>0.453108639272595</v>
+        <v>5.91211095973774</v>
       </c>
       <c r="AH11" t="n">
-        <v>0.0694029333978714</v>
+        <v>-0.895613718645758</v>
       </c>
       <c r="AI11" t="n">
-        <v>166.62976501752</v>
+        <v>-0.823422918814776</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.934940824974651</v>
+        <v>64.7608500031866</v>
       </c>
       <c r="AK11" t="n">
-        <v>-0.183693718308759</v>
+        <v>0.0115876780519277</v>
       </c>
       <c r="AL11" t="n">
-        <v>-0.586790574622009</v>
+        <v>-0.0794686588701281</v>
       </c>
       <c r="AM11" t="n">
-        <v>0.0906820991304916</v>
+        <v>-0.022730959003571</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>0.132832947960337</v>
+      </c>
+      <c r="AO11" t="n">
+        <v>0.482211586012499</v>
+      </c>
+      <c r="AP11" t="n">
+        <v>0.025794931752281</v>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.0316327784762719</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.00888449742549417</v>
+      </c>
+      <c r="AS11" t="n">
+        <v>-0.416902965091475</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>49</v>
+        <v>55</v>
       </c>
       <c r="B12" t="n">
-        <v>0.106287178707062</v>
+        <v>0.0792228006934863</v>
       </c>
       <c r="C12" t="n">
-        <v>0.0588055763397651</v>
+        <v>0.0627569214130735</v>
       </c>
       <c r="D12" t="n">
-        <v>0.171796636369892</v>
+        <v>0.16928729582152</v>
       </c>
       <c r="E12" t="n">
-        <v>0.554094433397117</v>
+        <v>0.181161651205074</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0585231889869436</v>
+        <v>0.0151993913420284</v>
       </c>
       <c r="G12" t="n">
-        <v>0.0250796492995931</v>
+        <v>0.0337106585056498</v>
       </c>
       <c r="H12" t="n">
-        <v>0.134849692953813</v>
+        <v>0.0663592388653425</v>
       </c>
       <c r="I12" t="n">
-        <v>0.14509785139417</v>
+        <v>0.12082021118173</v>
       </c>
       <c r="J12" t="n">
-        <v>0.386616207851143</v>
+        <v>0.467253145695357</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.0808845123938792</v>
+        <v>0.0122705756134747</v>
       </c>
       <c r="L12" t="n">
-        <v>0.43124139464155</v>
+        <v>0.198025239949699</v>
       </c>
       <c r="M12" t="n">
-        <v>0.109037215713351</v>
+        <v>0.0571106148616265</v>
       </c>
       <c r="N12" t="n">
-        <v>0.0165723088463988</v>
+        <v>-0.00197631555638445</v>
       </c>
       <c r="O12" t="n">
-        <v>0.0353163119822963</v>
+        <v>0.0331111192044257</v>
       </c>
       <c r="P12" t="n">
-        <v>0.180682108931934</v>
+        <v>0.094141686407852</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.126811716275148</v>
+        <v>0.0506071158844021</v>
       </c>
       <c r="R12" t="n">
-        <v>0.177400912505652</v>
+        <v>0.0855989607660336</v>
       </c>
       <c r="S12" t="n">
-        <v>0.162931327655325</v>
+        <v>0.0792228006934863</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.0559528674592195</v>
+        <v>0.025588352033364</v>
       </c>
       <c r="U12" t="n">
-        <v>1.48859703176717</v>
+        <v>-0.0158690518044377</v>
       </c>
       <c r="V12" t="n">
-        <v>0.302695896886023</v>
+        <v>-0.00954756689330399</v>
       </c>
       <c r="W12" t="n">
-        <v>1.29365625073829</v>
+        <v>1.02430888453424</v>
       </c>
       <c r="X12" t="n">
-        <v>0.00223508275950978</v>
+        <v>10.3825789897294</v>
       </c>
       <c r="Y12" t="n">
-        <v>0.0638621769674025</v>
+        <v>-11.8074921105374</v>
       </c>
       <c r="Z12" t="n">
-        <v>3.84404250287606</v>
+        <v>-12.7054687916566</v>
       </c>
       <c r="AA12" t="n">
-        <v>-11.4425639808256</v>
+        <v>0.615213205875665</v>
       </c>
       <c r="AB12" t="n">
-        <v>-13.2251076910851</v>
+        <v>-1.22766947552045</v>
       </c>
       <c r="AC12" t="n">
-        <v>0.017027687936325</v>
+        <v>-1.35410658786014</v>
       </c>
       <c r="AD12" t="n">
-        <v>0.274283284522867</v>
+        <v>0.168168106349812</v>
       </c>
       <c r="AE12" t="n">
-        <v>3.77293020223013</v>
+        <v>0.0792228006934863</v>
       </c>
       <c r="AF12" t="n">
-        <v>7.80705501253983</v>
+        <v>4.24082559502784</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.10194285291135</v>
+        <v>6.72187461778694</v>
       </c>
       <c r="AH12" t="n">
-        <v>0.515189470637316</v>
+        <v>3.20570944017448</v>
       </c>
       <c r="AI12" t="n">
-        <v>138.86489018101</v>
+        <v>1.13064796511604</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.633013630229546</v>
+        <v>69.5078139826724</v>
       </c>
       <c r="AK12" t="n">
-        <v>-1.17056340484263</v>
+        <v>0.0792228006934863</v>
       </c>
       <c r="AL12" t="n">
-        <v>-1.3485258279328</v>
+        <v>0.0495522387392417</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.230803181173616</v>
+        <v>-0.0605144058354366</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>0.283442369376223</v>
+      </c>
+      <c r="AO12" t="n">
+        <v>1.25678752951199</v>
+      </c>
+      <c r="AP12" t="n">
+        <v>0.0100053706656015</v>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.0696894773037612</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0.0122694085372572</v>
+      </c>
+      <c r="AS12" t="n">
+        <v>0.265324252837569</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="B13" t="n">
-        <v>-0.0465893749634942</v>
+        <v>-0.0490739711179799</v>
       </c>
       <c r="C13" t="n">
-        <v>-0.223220001999912</v>
+        <v>-0.330280240826589</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.224873212082442</v>
+        <v>-0.163792050368117</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.251159598303758</v>
+        <v>-0.167271902499466</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.0975987974180862</v>
+        <v>-0.0851775313067445</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.0409526200331871</v>
+        <v>-0.111206748686996</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.150672349505691</v>
+        <v>-0.133451925871853</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.211152717433232</v>
+        <v>-0.237554391414924</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.00990787078072184</v>
+        <v>-0.170995817172662</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.154639432268191</v>
+        <v>-0.162021848639044</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.271646526576622</v>
+        <v>-0.186937087540904</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.162530488057975</v>
+        <v>-0.116101471196711</v>
       </c>
       <c r="N13" t="n">
-        <v>-0.143604935679247</v>
+        <v>-0.146379752900888</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.024630600117232</v>
+        <v>-0.0352814659320229</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.208536841968602</v>
+        <v>-0.172749983022184</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0.137484078049976</v>
+        <v>-0.127267221710903</v>
       </c>
       <c r="R13" t="n">
-        <v>-0.208072535110238</v>
+        <v>-0.16932861076034</v>
       </c>
       <c r="S13" t="n">
-        <v>0.00140882235471387</v>
+        <v>-0.0490739711179799</v>
       </c>
       <c r="T13" t="n">
-        <v>0.0418464937381661</v>
+        <v>-0.0451321703004038</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.05198163700138</v>
+        <v>-0.00388917318968417</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.151733863241545</v>
+        <v>-0.010783841722055</v>
       </c>
       <c r="W13" t="n">
-        <v>-0.447027872714139</v>
+        <v>-0.63488960520175</v>
       </c>
       <c r="X13" t="n">
-        <v>0.0340348870538735</v>
+        <v>-8.88016008611467</v>
       </c>
       <c r="Y13" t="n">
-        <v>-0.028910315055723</v>
+        <v>10.5718083691601</v>
       </c>
       <c r="Z13" t="n">
-        <v>-6.81267968082047</v>
+        <v>-10.3132268136898</v>
       </c>
       <c r="AA13" t="n">
-        <v>10.1575564519124</v>
+        <v>-0.296919982786842</v>
       </c>
       <c r="AB13" t="n">
-        <v>-10.9514650212753</v>
+        <v>0.837274531912688</v>
       </c>
       <c r="AC13" t="n">
-        <v>-0.00291283281857747</v>
+        <v>1.8697104870729</v>
       </c>
       <c r="AD13" t="n">
-        <v>-0.031046905986031</v>
+        <v>0.010749126320787</v>
       </c>
       <c r="AE13" t="n">
-        <v>-2.85727085687985</v>
+        <v>-0.0490739711179799</v>
       </c>
       <c r="AF13" t="n">
-        <v>1.50508403781023</v>
+        <v>-3.68921628388639</v>
       </c>
       <c r="AG13" t="n">
-        <v>-0.404284631845628</v>
+        <v>2.44971914892797</v>
       </c>
       <c r="AH13" t="n">
-        <v>-0.100280015816208</v>
+        <v>-0.698329443036231</v>
       </c>
       <c r="AI13" t="n">
-        <v>8.93628752397186</v>
+        <v>-0.587401204304756</v>
       </c>
       <c r="AJ13" t="n">
-        <v>-0.305249157915723</v>
+        <v>-10.837588555778</v>
       </c>
       <c r="AK13" t="n">
-        <v>0.78307428994856</v>
+        <v>-0.0490739711179799</v>
       </c>
       <c r="AL13" t="n">
-        <v>1.80348416323166</v>
+        <v>-0.0127727968714012</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.00966474507527633</v>
+        <v>0.0412324619215205</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>-0.148420789500691</v>
+      </c>
+      <c r="AO13" t="n">
+        <v>-0.513037522362324</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>-0.00224041830810374</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>-0.0347804888684874</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>-0.00141794201922911</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>-0.0459642948242026</v>
       </c>
     </row>
   </sheetData>
